--- a/Vf/TABLE_4_5/Table_5_PanelB_MIDAS.xlsx
+++ b/Vf/TABLE_4_5/Table_5_PanelB_MIDAS.xlsx
@@ -484,13 +484,13 @@
         <v>1.043234044517219</v>
       </c>
       <c r="C4" t="n">
-        <v>1.122443564308768</v>
+        <v>1.122155908861306</v>
       </c>
       <c r="D4" t="n">
-        <v>1.124707770298013</v>
+        <v>1.123930647732461</v>
       </c>
       <c r="E4" t="n">
-        <v>1.036951252978058</v>
+        <v>1.036458178236607</v>
       </c>
     </row>
     <row r="5">
@@ -515,10 +515,10 @@
         <v>0.95</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9563726212146051</v>
+        <v>0.9280196814332935</v>
       </c>
       <c r="C6" t="n">
-        <v>1.053638780140705</v>
+        <v>1.052831595655682</v>
       </c>
       <c r="D6" t="n">
         <v>1.082470143422389</v>
